--- a/VerveStacks_UGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_UGA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_UGA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4F8F0CF-B9B0-4337-B8BC-3D2D80AF588F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3EC09D2-7159-4BC8-8A3C-2AD47C281B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,16 +826,106 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_014</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 14</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_solelc_spv_006</t>
@@ -844,148 +934,82 @@
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w212063751-220,e_w584663033-220,e_w171028597-220</t>
+  </si>
+  <si>
+    <t>e_w846731380-400,e_w600689855-220</t>
+  </si>
+  <si>
+    <t>e_w696954754-220,e_r17309135-220,e_w584663046-220</t>
+  </si>
+  <si>
+    <t>e_w1006639185-400</t>
+  </si>
+  <si>
+    <t>e_w846731380-400</t>
+  </si>
+  <si>
     <t>e_UG4-220,e_w696770566-220,e_w1006639185-400,e_w846731380-400</t>
   </si>
   <si>
+    <t>e_r17309135-220,e_UG4-220,e_w212063751-220,e_w696770566-220</t>
+  </si>
+  <si>
+    <t>e_w171028597-220,e_UG3-220,e_UG2-220,e_w600689855-220</t>
+  </si>
+  <si>
+    <t>e_UG3-220,e_w600689855-220</t>
+  </si>
+  <si>
+    <t>e_w212063751-220</t>
+  </si>
+  <si>
+    <t>e_w584663033-220,e_w584663033-400,e_w171028597-220</t>
+  </si>
+  <si>
+    <t>e_w171028597-220,e_w600689855-220,e_UG3-220</t>
+  </si>
+  <si>
+    <t>e_w846731380-400,e_w1006639185-400</t>
+  </si>
+  <si>
+    <t>e_w696954754-220,e_w584663046-220,e_w212063751-220</t>
+  </si>
+  <si>
+    <t>e_w212063751-220,e_w696770566-220,e_w584663033-220,e_w584663033-400</t>
+  </si>
+  <si>
     <t>e_w171028597-220,e_w846731380-400,e_w600689855-220,e_UG3-220</t>
   </si>
   <si>
-    <t>e_r17309135-220,e_UG4-220,e_w212063751-220,e_w696770566-220</t>
-  </si>
-  <si>
-    <t>e_w171028597-220,e_UG3-220,e_UG2-220,e_w600689855-220</t>
-  </si>
-  <si>
-    <t>e_w846731380-400</t>
-  </si>
-  <si>
-    <t>e_w846731380-400,e_w1006639185-400</t>
-  </si>
-  <si>
-    <t>e_w1006639185-400</t>
-  </si>
-  <si>
-    <t>e_w212063751-220,e_w584663033-220,e_w171028597-220</t>
-  </si>
-  <si>
-    <t>e_w846731380-400,e_w600689855-220</t>
-  </si>
-  <si>
-    <t>e_UG3-220,e_w600689855-220</t>
-  </si>
-  <si>
-    <t>e_w696954754-220,e_r17309135-220,e_w584663046-220</t>
-  </si>
-  <si>
-    <t>e_w584663033-220,e_w584663033-400,e_w171028597-220</t>
-  </si>
-  <si>
-    <t>e_w171028597-220,e_w600689855-220,e_UG3-220</t>
-  </si>
-  <si>
-    <t>e_w212063751-220</t>
-  </si>
-  <si>
-    <t>e_w696954754-220,e_w584663046-220,e_w212063751-220</t>
-  </si>
-  <si>
-    <t>e_w212063751-220,e_w696770566-220,e_w584663033-220,e_w584663033-400</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wonelc_won_002</t>
@@ -994,46 +1018,22 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w600689855-220</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
   </si>
   <si>
     <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w600689855-220</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -5990,7 +5990,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D116528F-B730-46BF-89FE-F55C2D065E07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F2BF4B-357C-47F3-8F15-CD721693AE3D}">
   <dimension ref="B9:AP27"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6186,16 +6186,16 @@
         <v>232</v>
       </c>
       <c r="Y11" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="Z11" t="s">
         <v>270</v>
       </c>
       <c r="AA11">
-        <v>0.99712828474993054</v>
+        <v>0.99532992211872329</v>
       </c>
       <c r="AB11">
-        <v>52.648112917939905</v>
+        <v>85.61809449007319</v>
       </c>
       <c r="AD11" t="s">
         <v>231</v>
@@ -6228,10 +6228,10 @@
         <v>274</v>
       </c>
       <c r="AO11">
-        <v>0.98685246979221208</v>
+        <v>0.98835919848200438</v>
       </c>
       <c r="AP11">
-        <v>241.0380538094461</v>
+        <v>213.4146944965857</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6296,16 +6296,16 @@
         <v>236</v>
       </c>
       <c r="Y12" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Z12" t="s">
         <v>271</v>
       </c>
       <c r="AA12">
-        <v>0.99177130598703001</v>
+        <v>0.98630571265287026</v>
       </c>
       <c r="AB12">
-        <v>150.85939023778275</v>
+        <v>251.06193469737815</v>
       </c>
       <c r="AD12" t="s">
         <v>231</v>
@@ -6335,13 +6335,13 @@
         <v>297</v>
       </c>
       <c r="AN12" t="s">
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="AO12">
-        <v>0.98556104331002803</v>
+        <v>0.98749920994696694</v>
       </c>
       <c r="AP12">
-        <v>264.71420598281912</v>
+        <v>229.18115097227223</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6406,16 +6406,16 @@
         <v>238</v>
       </c>
       <c r="Y13" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Z13" t="s">
         <v>272</v>
       </c>
       <c r="AA13">
-        <v>0.99653018249232661</v>
+        <v>0.99707110971625845</v>
       </c>
       <c r="AB13">
-        <v>63.613320974011444</v>
+        <v>53.696321868595874</v>
       </c>
       <c r="AD13" t="s">
         <v>231</v>
@@ -6442,16 +6442,16 @@
         <v>290</v>
       </c>
       <c r="AM13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AN13" t="s">
         <v>274</v>
       </c>
       <c r="AO13">
-        <v>0.98835919848200438</v>
+        <v>0.98556104331002803</v>
       </c>
       <c r="AP13">
-        <v>213.4146944965857</v>
+        <v>264.71420598281912</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6516,16 +6516,16 @@
         <v>240</v>
       </c>
       <c r="Y14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="Z14" t="s">
         <v>273</v>
       </c>
       <c r="AA14">
-        <v>0.99601637127870646</v>
+        <v>0.99399901741566254</v>
       </c>
       <c r="AB14">
-        <v>73.033193223714363</v>
+        <v>110.01801404618743</v>
       </c>
       <c r="AD14" t="s">
         <v>231</v>
@@ -6552,16 +6552,16 @@
         <v>292</v>
       </c>
       <c r="AM14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="AO14">
-        <v>0.98749920994696694</v>
+        <v>0.98397872490462623</v>
       </c>
       <c r="AP14">
-        <v>229.18115097227223</v>
+        <v>293.72337674851991</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6665,13 +6665,13 @@
         <v>301</v>
       </c>
       <c r="AN15" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="AO15">
-        <v>0.98397872490462623</v>
+        <v>0.98685246979221208</v>
       </c>
       <c r="AP15">
-        <v>293.72337674851991</v>
+        <v>241.0380538094461</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6736,16 +6736,16 @@
         <v>244</v>
       </c>
       <c r="Y16" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="AA16">
-        <v>0.99319041699561716</v>
+        <v>0.9931590433681845</v>
       </c>
       <c r="AB16">
-        <v>124.84235508035145</v>
+        <v>125.41753824995104</v>
       </c>
     </row>
     <row r="17" spans="2:28">
@@ -6810,16 +6810,16 @@
         <v>246</v>
       </c>
       <c r="Y17" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Z17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AA17">
-        <v>0.9931590433681845</v>
+        <v>0.99712828474993054</v>
       </c>
       <c r="AB17">
-        <v>125.41753824995104</v>
+        <v>52.648112917939905</v>
       </c>
     </row>
     <row r="18" spans="2:28">
@@ -6884,16 +6884,16 @@
         <v>248</v>
       </c>
       <c r="Y18" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Z18" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AA18">
-        <v>0.99532992211872329</v>
+        <v>0.99653018249232661</v>
       </c>
       <c r="AB18">
-        <v>85.61809449007319</v>
+        <v>63.613320974011444</v>
       </c>
     </row>
     <row r="19" spans="2:28">
@@ -6958,16 +6958,16 @@
         <v>250</v>
       </c>
       <c r="Y19" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="Z19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AA19">
-        <v>0.98630571265287026</v>
+        <v>0.99601637127870646</v>
       </c>
       <c r="AB19">
-        <v>251.06193469737815</v>
+        <v>73.033193223714363</v>
       </c>
     </row>
     <row r="20" spans="2:28">
@@ -7035,7 +7035,7 @@
         <v>219</v>
       </c>
       <c r="Z20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AA20">
         <v>0.99814287491480569</v>
@@ -7106,16 +7106,16 @@
         <v>254</v>
       </c>
       <c r="Y21" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="Z21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AA21">
-        <v>0.99707110971625845</v>
+        <v>0.99670639767963631</v>
       </c>
       <c r="AB21">
-        <v>53.696321868595874</v>
+        <v>60.38270920666691</v>
       </c>
     </row>
     <row r="22" spans="2:28">
@@ -7180,16 +7180,16 @@
         <v>256</v>
       </c>
       <c r="Y22" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="Z22" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AA22">
-        <v>0.99399901741566254</v>
+        <v>0.99743813662378511</v>
       </c>
       <c r="AB22">
-        <v>110.01801404618743</v>
+        <v>46.967495230606502</v>
       </c>
     </row>
     <row r="23" spans="2:28">
@@ -7254,16 +7254,16 @@
         <v>258</v>
       </c>
       <c r="Y23" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="Z23" t="s">
         <v>281</v>
       </c>
       <c r="AA23">
-        <v>0.99743813662378511</v>
+        <v>0.99700516323982269</v>
       </c>
       <c r="AB23">
-        <v>46.967495230606502</v>
+        <v>54.905340603249918</v>
       </c>
     </row>
     <row r="24" spans="2:28">
@@ -7328,16 +7328,16 @@
         <v>260</v>
       </c>
       <c r="Y24" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Z24" t="s">
         <v>282</v>
       </c>
       <c r="AA24">
-        <v>0.99700516323982269</v>
+        <v>0.99319041699561716</v>
       </c>
       <c r="AB24">
-        <v>54.905340603249918</v>
+        <v>124.84235508035145</v>
       </c>
     </row>
     <row r="25" spans="2:28">
@@ -7402,16 +7402,16 @@
         <v>262</v>
       </c>
       <c r="Y25" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="Z25" t="s">
         <v>283</v>
       </c>
       <c r="AA25">
-        <v>0.99670639767963631</v>
+        <v>0.99689242857794957</v>
       </c>
       <c r="AB25">
-        <v>60.38270920666691</v>
+        <v>56.972142737590893</v>
       </c>
     </row>
     <row r="26" spans="2:28">
@@ -7476,16 +7476,16 @@
         <v>264</v>
       </c>
       <c r="Y26" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="Z26" t="s">
         <v>284</v>
       </c>
       <c r="AA26">
-        <v>0.99689242857794957</v>
+        <v>0.99606378156258346</v>
       </c>
       <c r="AB26">
-        <v>56.972142737590893</v>
+        <v>72.164004685969289</v>
       </c>
     </row>
     <row r="27" spans="2:28">
@@ -7550,16 +7550,16 @@
         <v>266</v>
       </c>
       <c r="Y27" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="Z27" t="s">
         <v>285</v>
       </c>
       <c r="AA27">
-        <v>0.99606378156258346</v>
+        <v>0.99177130598703001</v>
       </c>
       <c r="AB27">
-        <v>72.164004685969289</v>
+        <v>150.85939023778275</v>
       </c>
     </row>
   </sheetData>
@@ -7568,7 +7568,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F27C042-25E2-48E3-A41C-5A10CA5E0EBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F66E467E-4F84-4214-983A-F5C3EF84BC36}">
   <dimension ref="B9:M15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7641,7 +7641,7 @@
         <v>302</v>
       </c>
       <c r="K11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L11">
         <v>0.12805123607019345</v>
@@ -7676,7 +7676,7 @@
         <v>304</v>
       </c>
       <c r="K12" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="L12">
         <v>0.23616721044045683</v>
@@ -7711,7 +7711,7 @@
         <v>306</v>
       </c>
       <c r="K13" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L13">
         <v>5.9871287451504572E-2</v>
@@ -7746,7 +7746,7 @@
         <v>308</v>
       </c>
       <c r="K14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L14">
         <v>0.52862813293405375</v>
@@ -7781,7 +7781,7 @@
         <v>310</v>
       </c>
       <c r="K15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L15">
         <v>2.0712289716337019E-2</v>
@@ -7796,7 +7796,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{311D8F3F-02F3-439D-878F-054FE8A50BFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142DAFC4-67D5-41FA-9512-FDB894FF887E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9613,7 +9613,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B655C4-A29A-4750-AC92-213634D10295}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20DEED5A-57AA-4588-821A-6417F58BA436}">
   <dimension ref="B2:M17"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9790,7 +9790,7 @@
         <v>343</v>
       </c>
       <c r="C8" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D8" t="s">
         <v>344</v>
@@ -9825,7 +9825,7 @@
         <v>344</v>
       </c>
       <c r="D9" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -9982,7 +9982,7 @@
         <v>354</v>
       </c>
       <c r="C14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D14" t="s">
         <v>355</v>
@@ -10017,7 +10017,7 @@
         <v>355</v>
       </c>
       <c r="D15" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E15">
         <v>1</v>
